--- a/椙山改修/261030_課題リスト（1030_定例後）.xlsx
+++ b/椙山改修/261030_課題リスト（1030_定例後）.xlsx
@@ -261,7 +261,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -776,6 +776,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1597,34 +1600,34 @@
       <c r="Q10" s="1" t="n"/>
     </row>
     <row r="11" ht="101" customFormat="1" customHeight="1" s="98">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="149" t="n">
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="133" t="n">
         <v>46283</v>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="39" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="37" t="inlineStr">
         <is>
           <t>アスベスト含有建材事前調査を10月初旬に実施予定</t>
         </is>
       </c>
-      <c r="K11" s="89" t="inlineStr">
+      <c r="K11" s="40" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="L11" s="33" t="inlineStr">
+      <c r="L11" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1648,14 +1651,16 @@
           </r>
         </is>
       </c>
-      <c r="M11" s="160" t="n">
+      <c r="M11" s="175" t="n">
         <v>580000</v>
       </c>
-      <c r="N11" s="149" t="n">
+      <c r="N11" s="133" t="n">
         <v>46311</v>
       </c>
-      <c r="O11" s="152" t="n"/>
-      <c r="P11" s="20" t="n"/>
+      <c r="O11" s="136" t="n">
+        <v>46323</v>
+      </c>
+      <c r="P11" s="45" t="n"/>
       <c r="Q11" s="1" t="n"/>
     </row>
     <row r="12" ht="53.1" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1030_定例後）.xlsx
+++ b/椙山改修/261030_課題リスト（1030_定例後）.xlsx
@@ -1945,55 +1945,72 @@
       <c r="P17" s="114" t="n"/>
       <c r="Q17" s="1" t="n"/>
     </row>
-    <row r="18" ht="75" customFormat="1" customHeight="1" s="98">
-      <c r="A18" s="15" t="n">
+    <row r="18" ht="88" customFormat="1" customHeight="1" s="98">
+      <c r="A18" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="149" t="n">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="133" t="n">
         <v>46297</v>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="39" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="J18" s="37" t="inlineStr">
         <is>
           <t>2階プランターの方針（内部は撤去なし、外部は撤去してガラスと同面で塞ぎたい）</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K18" s="36" t="inlineStr">
         <is>
           <t>NS
 SJ
 SC</t>
         </is>
       </c>
-      <c r="L18" s="33" t="inlineStr">
-        <is>
-          <t>・10/2 第3回分科会　方針はガラス同面で塞ぐ（フィルムが張れるもの）。詳細は解体後に確認し、仕上は既存ガラスに合わせたフィルムとする
+      <c r="L18" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">・10/2 第3回分科会　方針はガラス同面で塞ぐ（フィルムが張れるもの）。詳細は解体後に確認し、仕上は既存ガラスに合わせたフィルムとする
 ・10/9 第2回定例　SCより食堂側（外部）は撤去予定。室内側は現状運用上使用していないため、要望があれば撤去見積を提出すると説明
-・同　SJより見積を確認してから判断すると回答</t>
-        </is>
-      </c>
-      <c r="M18" s="160" t="n">
+・同　SJより見積を確認してから判断すると回答
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <color rgb="FFFF0000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>・10/30　解決、撤去しない（小山さん確認）</t>
+          </r>
+        </is>
+      </c>
+      <c r="M18" s="175" t="n">
         <v>650000</v>
       </c>
-      <c r="N18" s="149" t="n">
+      <c r="N18" s="133" t="n">
         <v>46332</v>
       </c>
-      <c r="O18" s="152" t="n"/>
-      <c r="P18" s="20" t="n"/>
+      <c r="O18" s="136" t="n">
+        <v>46325</v>
+      </c>
+      <c r="P18" s="45" t="n"/>
       <c r="Q18" s="1" t="n"/>
     </row>
     <row r="19" ht="61.95" customFormat="1" customHeight="1" s="98">
